--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/26.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/26.xlsx
@@ -426,13 +426,13 @@
         <v>-10.36574440678929</v>
       </c>
       <c r="E2">
-        <v>-7.236154848466242</v>
+        <v>-9.21235373456954</v>
       </c>
       <c r="F2">
-        <v>-6.350985750932654</v>
+        <v>-6.036760729845017</v>
       </c>
       <c r="G2">
-        <v>-7.28513469565988</v>
+        <v>-8.984758843885089</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.55123748919446</v>
       </c>
       <c r="E3">
-        <v>-7.584729606732661</v>
+        <v>-9.34093975401734</v>
       </c>
       <c r="F3">
-        <v>-6.057808717182749</v>
+        <v>-6.015914035786165</v>
       </c>
       <c r="G3">
-        <v>-7.446060314323852</v>
+        <v>-8.909930583060943</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.10369338541567</v>
       </c>
       <c r="E4">
-        <v>-8.453508288156204</v>
+        <v>-9.348198897851637</v>
       </c>
       <c r="F4">
-        <v>-6.148142182458035</v>
+        <v>-5.567498879833125</v>
       </c>
       <c r="G4">
-        <v>-7.152981028277713</v>
+        <v>-9.152073815439856</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.78670083000657</v>
       </c>
       <c r="E5">
-        <v>-9.191214817901736</v>
+        <v>-10.21825460894534</v>
       </c>
       <c r="F5">
-        <v>-6.075045386100202</v>
+        <v>-5.648060923224988</v>
       </c>
       <c r="G5">
-        <v>-7.077467484526937</v>
+        <v>-8.508361409147348</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.53924451569112</v>
       </c>
       <c r="E6">
-        <v>-8.825454500776209</v>
+        <v>-11.08617288030743</v>
       </c>
       <c r="F6">
-        <v>-6.043373586821565</v>
+        <v>-5.476086051831991</v>
       </c>
       <c r="G6">
-        <v>-7.784888029177179</v>
+        <v>-8.915005649372645</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.21483374139658</v>
       </c>
       <c r="E7">
-        <v>-9.63399542094972</v>
+        <v>-11.68441599603874</v>
       </c>
       <c r="F7">
-        <v>-5.779526143518881</v>
+        <v>-5.332687370733368</v>
       </c>
       <c r="G7">
-        <v>-6.848275106297654</v>
+        <v>-8.945697717067228</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-19.69954574369514</v>
       </c>
       <c r="E8">
-        <v>-10.57096386398076</v>
+        <v>-11.36407174473613</v>
       </c>
       <c r="F8">
-        <v>-5.661303204526141</v>
+        <v>-5.469776377324867</v>
       </c>
       <c r="G8">
-        <v>-7.175757581587899</v>
+        <v>-8.340566408489387</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.85843471138462</v>
       </c>
       <c r="E9">
-        <v>-11.49846326786177</v>
+        <v>-12.54341317360571</v>
       </c>
       <c r="F9">
-        <v>-5.326231075195949</v>
+        <v>-5.164544526945722</v>
       </c>
       <c r="G9">
-        <v>-7.369566849093452</v>
+        <v>-9.342986355598546</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.58674272304249</v>
       </c>
       <c r="E10">
-        <v>-11.97672446475985</v>
+        <v>-13.15189516906836</v>
       </c>
       <c r="F10">
-        <v>-5.378964944058166</v>
+        <v>-4.987876125848463</v>
       </c>
       <c r="G10">
-        <v>-7.113820585093674</v>
+        <v>-8.761081834524232</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-21.79973268900149</v>
       </c>
       <c r="E11">
-        <v>-12.72388191975939</v>
+        <v>-14.46288839428893</v>
       </c>
       <c r="F11">
-        <v>-5.334122103075018</v>
+        <v>-4.747623071279717</v>
       </c>
       <c r="G11">
-        <v>-6.694026857986391</v>
+        <v>-9.184427776995152</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-21.4570360529205</v>
       </c>
       <c r="E12">
-        <v>-12.80810700782805</v>
+        <v>-13.61134961341259</v>
       </c>
       <c r="F12">
-        <v>-5.241671330718176</v>
+        <v>-4.704738490836787</v>
       </c>
       <c r="G12">
-        <v>-5.872183927862319</v>
+        <v>-8.156546424143459</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-20.55649172238774</v>
       </c>
       <c r="E13">
-        <v>-13.80917600043767</v>
+        <v>-14.97345119628372</v>
       </c>
       <c r="F13">
-        <v>-5.147718728260059</v>
+        <v>-4.692106716311497</v>
       </c>
       <c r="G13">
-        <v>-6.142271475138219</v>
+        <v>-7.87418668455348</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.14767501961053</v>
       </c>
       <c r="E14">
-        <v>-14.99847554365011</v>
+        <v>-15.31450868769741</v>
       </c>
       <c r="F14">
-        <v>-4.62695396334651</v>
+        <v>-4.180576591204358</v>
       </c>
       <c r="G14">
-        <v>-5.988254965014707</v>
+        <v>-7.43203353287396</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-17.31938823964652</v>
       </c>
       <c r="E15">
-        <v>-14.13326529974461</v>
+        <v>-14.48584322903381</v>
       </c>
       <c r="F15">
-        <v>-4.532151455933121</v>
+        <v>-3.968570865071074</v>
       </c>
       <c r="G15">
-        <v>-5.703855929372536</v>
+        <v>-7.596438534899707</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.19616990690601</v>
       </c>
       <c r="E16">
-        <v>-14.98903367534412</v>
+        <v>-15.96033700830132</v>
       </c>
       <c r="F16">
-        <v>-4.251943756425146</v>
+        <v>-4.077711583859521</v>
       </c>
       <c r="G16">
-        <v>-4.878997092262188</v>
+        <v>-6.980726722778355</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.92850422654421</v>
       </c>
       <c r="E17">
-        <v>-15.26543361487628</v>
+        <v>-16.55245762717425</v>
       </c>
       <c r="F17">
-        <v>-4.268023196080887</v>
+        <v>-3.653937873037558</v>
       </c>
       <c r="G17">
-        <v>-4.061116885148624</v>
+        <v>-5.937395053894883</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.67675409532165</v>
       </c>
       <c r="E18">
-        <v>-15.82811915269937</v>
+        <v>-17.40844336952613</v>
       </c>
       <c r="F18">
-        <v>-3.559421980745537</v>
+        <v>-3.079002850185339</v>
       </c>
       <c r="G18">
-        <v>-3.844070898502926</v>
+        <v>-6.357106017363685</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.594016241652259</v>
       </c>
       <c r="E19">
-        <v>-17.52505157522364</v>
+        <v>-17.57390022434438</v>
       </c>
       <c r="F19">
-        <v>-3.658233786388476</v>
+        <v>-2.851226665437558</v>
       </c>
       <c r="G19">
-        <v>-3.30914301863087</v>
+        <v>-6.201808326116473</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.811930279246555</v>
       </c>
       <c r="E20">
-        <v>-18.9757844513729</v>
+        <v>-18.71986679977742</v>
       </c>
       <c r="F20">
-        <v>-2.999926069546695</v>
+        <v>-2.854119324408134</v>
       </c>
       <c r="G20">
-        <v>-4.461533989214552</v>
+        <v>-6.856144273044501</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.421176763343551</v>
       </c>
       <c r="E21">
-        <v>-18.25572991330927</v>
+        <v>-19.98247780870004</v>
       </c>
       <c r="F21">
-        <v>-2.874016709423378</v>
+        <v>-2.087242462285839</v>
       </c>
       <c r="G21">
-        <v>-4.683598762897785</v>
+        <v>-6.500992258137028</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.471854885199649</v>
       </c>
       <c r="E22">
-        <v>-18.54178003095178</v>
+        <v>-20.17227973978353</v>
       </c>
       <c r="F22">
-        <v>-2.735322326805254</v>
+        <v>-2.102616961281798</v>
       </c>
       <c r="G22">
-        <v>-4.021469791770312</v>
+        <v>-6.273283004309338</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.968662991181774</v>
       </c>
       <c r="E23">
-        <v>-18.61838369726553</v>
+        <v>-20.39596371339241</v>
       </c>
       <c r="F23">
-        <v>-3.051447208531213</v>
+        <v>-2.107061152397817</v>
       </c>
       <c r="G23">
-        <v>-4.385904576369902</v>
+        <v>-6.099058924214113</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.874399078837072</v>
       </c>
       <c r="E24">
-        <v>-19.80404687584982</v>
+        <v>-20.71690572326402</v>
       </c>
       <c r="F24">
-        <v>-1.873917975247299</v>
+        <v>-1.642942635589907</v>
       </c>
       <c r="G24">
-        <v>-4.667787597402226</v>
+        <v>-6.30761336155158</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.12933934265562</v>
       </c>
       <c r="E25">
-        <v>-19.9188074641522</v>
+        <v>-20.86008248596454</v>
       </c>
       <c r="F25">
-        <v>-2.281404326195418</v>
+        <v>-2.021348320495346</v>
       </c>
       <c r="G25">
-        <v>-4.610290042476164</v>
+        <v>-7.276629904169492</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.655940503583994</v>
       </c>
       <c r="E26">
-        <v>-21.08692280595676</v>
+        <v>-20.4998650210244</v>
       </c>
       <c r="F26">
-        <v>-2.230458902555845</v>
+        <v>-1.729730688381211</v>
       </c>
       <c r="G26">
-        <v>-4.653439693035025</v>
+        <v>-6.795164024211126</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.37184240068697</v>
       </c>
       <c r="E27">
-        <v>-20.43362250324019</v>
+        <v>-20.98623671487022</v>
       </c>
       <c r="F27">
-        <v>-2.098608491419651</v>
+        <v>-1.669320338797252</v>
       </c>
       <c r="G27">
-        <v>-5.896102619383553</v>
+        <v>-7.142883864382936</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.200670301687904</v>
       </c>
       <c r="E28">
-        <v>-20.4127869943309</v>
+        <v>-21.04235356477327</v>
       </c>
       <c r="F28">
-        <v>-1.898966977140553</v>
+        <v>-1.953599464089986</v>
       </c>
       <c r="G28">
-        <v>-6.019837569459353</v>
+        <v>-7.145691207000239</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.072496230681607</v>
       </c>
       <c r="E29">
-        <v>-20.97582575312658</v>
+        <v>-20.50393611915729</v>
       </c>
       <c r="F29">
-        <v>-1.89437367989203</v>
+        <v>-1.890768624955047</v>
       </c>
       <c r="G29">
-        <v>-5.171056730282232</v>
+        <v>-6.455760274433966</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.927547191996808</v>
       </c>
       <c r="E30">
-        <v>-20.65959788469695</v>
+        <v>-21.46045398447945</v>
       </c>
       <c r="F30">
-        <v>-2.173637040560813</v>
+        <v>-1.932222614893342</v>
       </c>
       <c r="G30">
-        <v>-5.829514306406653</v>
+        <v>-7.212438426163024</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.721379667708726</v>
       </c>
       <c r="E31">
-        <v>-20.13568514132755</v>
+        <v>-21.37011545650043</v>
       </c>
       <c r="F31">
-        <v>-2.300783153216509</v>
+        <v>-2.296715040901361</v>
       </c>
       <c r="G31">
-        <v>-5.994776739727071</v>
+        <v>-6.669598342452109</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.420945171270647</v>
       </c>
       <c r="E32">
-        <v>-20.41499236117264</v>
+        <v>-20.8283559970668</v>
       </c>
       <c r="F32">
-        <v>-2.497411066884223</v>
+        <v>-2.383866746982494</v>
       </c>
       <c r="G32">
-        <v>-5.630871642413764</v>
+        <v>-6.633500153891896</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.01163976031307</v>
       </c>
       <c r="E33">
-        <v>-18.93692108743907</v>
+        <v>-20.39573276121802</v>
       </c>
       <c r="F33">
-        <v>-2.580715834746755</v>
+        <v>-2.027709353781444</v>
       </c>
       <c r="G33">
-        <v>-5.166137259610875</v>
+        <v>-5.968630051057906</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.49134038992543</v>
       </c>
       <c r="E34">
-        <v>-18.5545457991794</v>
+        <v>-19.91530242527026</v>
       </c>
       <c r="F34">
-        <v>-2.717834662564754</v>
+        <v>-2.225173090158582</v>
       </c>
       <c r="G34">
-        <v>-4.904710099465707</v>
+        <v>-5.645669780974306</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.86686359274568</v>
       </c>
       <c r="E35">
-        <v>-18.38727755475808</v>
+        <v>-19.05195791265592</v>
       </c>
       <c r="F35">
-        <v>-2.257158840682879</v>
+        <v>-2.269841145619739</v>
       </c>
       <c r="G35">
-        <v>-5.65314499280198</v>
+        <v>-5.957278190403746</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.15203573329301</v>
       </c>
       <c r="E36">
-        <v>-18.72980680022426</v>
+        <v>-19.78454726677279</v>
       </c>
       <c r="F36">
-        <v>-2.209580730535686</v>
+        <v>-2.37995353937167</v>
       </c>
       <c r="G36">
-        <v>-3.7963129685534</v>
+        <v>-5.754474170667993</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.36283164792344</v>
       </c>
       <c r="E37">
-        <v>-19.1262158294337</v>
+        <v>-19.14492295555939</v>
       </c>
       <c r="F37">
-        <v>-2.475987000745619</v>
+        <v>-2.259747488816628</v>
       </c>
       <c r="G37">
-        <v>-4.933578056568153</v>
+        <v>-5.436221496341236</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.50978235311115</v>
       </c>
       <c r="E38">
-        <v>-18.56857954012917</v>
+        <v>-19.08674564998285</v>
       </c>
       <c r="F38">
-        <v>-2.124502428063761</v>
+        <v>-2.214954349877647</v>
       </c>
       <c r="G38">
-        <v>-4.122550678720879</v>
+        <v>-5.096645598196034</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.60009157929341</v>
       </c>
       <c r="E39">
-        <v>-17.9563072119221</v>
+        <v>-19.28986582312289</v>
       </c>
       <c r="F39">
-        <v>-2.332373772489671</v>
+        <v>-2.345031226404448</v>
       </c>
       <c r="G39">
-        <v>-4.640323311608432</v>
+        <v>-4.471528526197612</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.63282644912702</v>
       </c>
       <c r="E40">
-        <v>-17.12172756620449</v>
+        <v>-18.93629162955201</v>
       </c>
       <c r="F40">
-        <v>-2.773562251220688</v>
+        <v>-2.446864087965396</v>
       </c>
       <c r="G40">
-        <v>-3.198560865982595</v>
+        <v>-4.654909575254461</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.60057221565082</v>
       </c>
       <c r="E41">
-        <v>-16.74611328963827</v>
+        <v>-18.95244922481137</v>
       </c>
       <c r="F41">
-        <v>-2.216623510194288</v>
+        <v>-2.361485916493657</v>
       </c>
       <c r="G41">
-        <v>-3.378432736767816</v>
+        <v>-4.286141286543965</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.49615273401831</v>
       </c>
       <c r="E42">
-        <v>-16.75412868863184</v>
+        <v>-17.89376445740217</v>
       </c>
       <c r="F42">
-        <v>-2.657310826646611</v>
+        <v>-2.490547214584626</v>
       </c>
       <c r="G42">
-        <v>-3.685757300269439</v>
+        <v>-4.402947264806071</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.3105149377187</v>
       </c>
       <c r="E43">
-        <v>-16.57767217044896</v>
+        <v>-17.58090577363425</v>
       </c>
       <c r="F43">
-        <v>-2.633630287702782</v>
+        <v>-2.344228538391135</v>
       </c>
       <c r="G43">
-        <v>-3.282105793211642</v>
+        <v>-4.119389107730875</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.03927833675393</v>
       </c>
       <c r="E44">
-        <v>-15.98842260409689</v>
+        <v>-17.06040297119262</v>
       </c>
       <c r="F44">
-        <v>-2.229321554111801</v>
+        <v>-2.58808830463167</v>
       </c>
       <c r="G44">
-        <v>-3.075279460645675</v>
+        <v>-4.455194294506848</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.6869389496066</v>
       </c>
       <c r="E45">
-        <v>-15.90480433154526</v>
+        <v>-16.62034850949725</v>
       </c>
       <c r="F45">
-        <v>-3.167385510227032</v>
+        <v>-2.807912162312575</v>
       </c>
       <c r="G45">
-        <v>-2.887078257283647</v>
+        <v>-4.358529675305669</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.26639085070678</v>
       </c>
       <c r="E46">
-        <v>-15.05807479006506</v>
+        <v>-16.59376636707222</v>
       </c>
       <c r="F46">
-        <v>-2.778175429286879</v>
+        <v>-2.507520462667987</v>
       </c>
       <c r="G46">
-        <v>-2.540325096409304</v>
+        <v>-4.087832987650542</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.7982337695535</v>
       </c>
       <c r="E47">
-        <v>-14.79954873744117</v>
+        <v>-16.54792462469258</v>
       </c>
       <c r="F47">
-        <v>-2.94138120335384</v>
+        <v>-2.976235590194032</v>
       </c>
       <c r="G47">
-        <v>-3.126016881580545</v>
+        <v>-4.408045504936548</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.311769859875175</v>
       </c>
       <c r="E48">
-        <v>-14.96420405236006</v>
+        <v>-15.40319432266362</v>
       </c>
       <c r="F48">
-        <v>-2.870302309989226</v>
+        <v>-3.088904325751001</v>
       </c>
       <c r="G48">
-        <v>-3.283016193234942</v>
+        <v>-3.701502254854212</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.836643493400519</v>
       </c>
       <c r="E49">
-        <v>-14.13216035208674</v>
+        <v>-16.00837506057468</v>
       </c>
       <c r="F49">
-        <v>-3.375368684252321</v>
+        <v>-3.144632742774338</v>
       </c>
       <c r="G49">
-        <v>-2.40270902888734</v>
+        <v>-4.015649852712273</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.404743338370862</v>
       </c>
       <c r="E50">
-        <v>-14.14144372380246</v>
+        <v>-15.92272350319361</v>
       </c>
       <c r="F50">
-        <v>-3.312409448169947</v>
+        <v>-3.132109484378815</v>
       </c>
       <c r="G50">
-        <v>-3.339216014309609</v>
+        <v>-3.625766904552306</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.042753861506748</v>
       </c>
       <c r="E51">
-        <v>-14.21404421909343</v>
+        <v>-14.72351113037837</v>
       </c>
       <c r="F51">
-        <v>-3.448095200381103</v>
+        <v>-3.447675218107884</v>
       </c>
       <c r="G51">
-        <v>-2.995419170601836</v>
+        <v>-3.757377642466031</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.767345001441742</v>
       </c>
       <c r="E52">
-        <v>-13.55016540109495</v>
+        <v>-15.35042401505224</v>
       </c>
       <c r="F52">
-        <v>-3.705149202613429</v>
+        <v>-3.211419036257645</v>
       </c>
       <c r="G52">
-        <v>-2.326000378196888</v>
+        <v>-4.03823770492672</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.587694088726761</v>
       </c>
       <c r="E53">
-        <v>-14.0280507346504</v>
+        <v>-14.50565530281737</v>
       </c>
       <c r="F53">
-        <v>-3.531090158834988</v>
+        <v>-3.117743108512063</v>
       </c>
       <c r="G53">
-        <v>-2.466774706163316</v>
+        <v>-4.195700492956616</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.504019255565376</v>
       </c>
       <c r="E54">
-        <v>-13.56633658177634</v>
+        <v>-14.93052126269101</v>
       </c>
       <c r="F54">
-        <v>-3.668358092785492</v>
+        <v>-3.545594043690605</v>
       </c>
       <c r="G54">
-        <v>-2.248328358754507</v>
+        <v>-4.18827493931203</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.509437823870573</v>
       </c>
       <c r="E55">
-        <v>-12.8972862464611</v>
+        <v>-14.48185364343305</v>
       </c>
       <c r="F55">
-        <v>-3.942279312073621</v>
+        <v>-3.397153918578545</v>
       </c>
       <c r="G55">
-        <v>-2.995869404795177</v>
+        <v>-3.890193418956053</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.594744222393315</v>
       </c>
       <c r="E56">
-        <v>-12.76447968923815</v>
+        <v>-14.27259285953861</v>
       </c>
       <c r="F56">
-        <v>-3.739899215160868</v>
+        <v>-3.810978108525482</v>
       </c>
       <c r="G56">
-        <v>-2.753097168763803</v>
+        <v>-3.793009044105208</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.746055866292777</v>
       </c>
       <c r="E57">
-        <v>-12.24164925115658</v>
+        <v>-13.54094542801534</v>
       </c>
       <c r="F57">
-        <v>-3.706366074328141</v>
+        <v>-3.541249256662922</v>
       </c>
       <c r="G57">
-        <v>-3.021228183625994</v>
+        <v>-3.833977045153688</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.945298314598607</v>
       </c>
       <c r="E58">
-        <v>-12.80278152239503</v>
+        <v>-14.07272865921007</v>
       </c>
       <c r="F58">
-        <v>-3.424123904478891</v>
+        <v>-3.673253744136037</v>
       </c>
       <c r="G58">
-        <v>-3.409141357190095</v>
+        <v>-3.865569581234953</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.175455608408816</v>
       </c>
       <c r="E59">
-        <v>-11.2951528988134</v>
+        <v>-13.7682838801484</v>
       </c>
       <c r="F59">
-        <v>-3.439851287988442</v>
+        <v>-3.498218055189696</v>
       </c>
       <c r="G59">
-        <v>-2.872170870720309</v>
+        <v>-3.976893296084025</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.415254916304534</v>
       </c>
       <c r="E60">
-        <v>-10.67236545396052</v>
+        <v>-13.03738817531041</v>
       </c>
       <c r="F60">
-        <v>-3.723736110397444</v>
+        <v>-3.63324028511121</v>
       </c>
       <c r="G60">
-        <v>-2.82578681716958</v>
+        <v>-3.839952579852073</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.645327721162772</v>
       </c>
       <c r="E61">
-        <v>-10.90194550072738</v>
+        <v>-12.73039386538242</v>
       </c>
       <c r="F61">
-        <v>-3.835860608570774</v>
+        <v>-3.899909976155232</v>
       </c>
       <c r="G61">
-        <v>-3.18409047143044</v>
+        <v>-4.579866128970262</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.848165956377057</v>
       </c>
       <c r="E62">
-        <v>-10.27116529925096</v>
+        <v>-13.52890421562894</v>
       </c>
       <c r="F62">
-        <v>-4.048019582673575</v>
+        <v>-3.905927236969168</v>
       </c>
       <c r="G62">
-        <v>-3.102151158787939</v>
+        <v>-4.409459107881816</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.010198411773356</v>
       </c>
       <c r="E63">
-        <v>-12.17635318443998</v>
+        <v>-13.3372410817283</v>
       </c>
       <c r="F63">
-        <v>-3.859834389575195</v>
+        <v>-3.913687382798593</v>
       </c>
       <c r="G63">
-        <v>-4.065956902727038</v>
+        <v>-4.682032874857709</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.125046811644534</v>
       </c>
       <c r="E64">
-        <v>-10.76440668816642</v>
+        <v>-12.36382747988353</v>
       </c>
       <c r="F64">
-        <v>-3.996655005128186</v>
+        <v>-4.085619179086645</v>
       </c>
       <c r="G64">
-        <v>-3.238158301177817</v>
+        <v>-3.925311686036641</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.192402817200502</v>
       </c>
       <c r="E65">
-        <v>-11.35900891079556</v>
+        <v>-13.47451271432281</v>
       </c>
       <c r="F65">
-        <v>-4.398776020408373</v>
+        <v>-3.86865981588462</v>
       </c>
       <c r="G65">
-        <v>-3.28788269517767</v>
+        <v>-4.177631535403274</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.213021686906206</v>
       </c>
       <c r="E66">
-        <v>-11.25930549856868</v>
+        <v>-12.82211810640778</v>
       </c>
       <c r="F66">
-        <v>-3.806915794782154</v>
+        <v>-4.025384443392078</v>
       </c>
       <c r="G66">
-        <v>-3.972702145431308</v>
+        <v>-4.13894450023135</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.192452288223071</v>
       </c>
       <c r="E67">
-        <v>-10.18885122721354</v>
+        <v>-12.74409702772963</v>
       </c>
       <c r="F67">
-        <v>-3.820289786500352</v>
+        <v>-4.028292012975905</v>
       </c>
       <c r="G67">
-        <v>-3.996756569319653</v>
+        <v>-4.21784804261434</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.135921533362882</v>
       </c>
       <c r="E68">
-        <v>-10.8389634842287</v>
+        <v>-12.39013791386809</v>
       </c>
       <c r="F68">
-        <v>-4.080499040169941</v>
+        <v>-3.97588120740078</v>
       </c>
       <c r="G68">
-        <v>-3.224326841914742</v>
+        <v>-4.594101474789128</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.047594124721762</v>
       </c>
       <c r="E69">
-        <v>-10.21296987977839</v>
+        <v>-11.97182465588355</v>
       </c>
       <c r="F69">
-        <v>-4.123804431253493</v>
+        <v>-3.983061496048246</v>
       </c>
       <c r="G69">
-        <v>-3.108113451304166</v>
+        <v>-4.00249043419367</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.933500171538473</v>
       </c>
       <c r="E70">
-        <v>-11.3096168447939</v>
+        <v>-12.46437771674984</v>
       </c>
       <c r="F70">
-        <v>-4.417479727996183</v>
+        <v>-4.145128264936358</v>
       </c>
       <c r="G70">
-        <v>-3.082102495002113</v>
+        <v>-4.376098740482581</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.797556737277811</v>
       </c>
       <c r="E71">
-        <v>-11.22596687292421</v>
+        <v>-12.77169354833237</v>
       </c>
       <c r="F71">
-        <v>-4.420678054538391</v>
+        <v>-4.40179956142859</v>
       </c>
       <c r="G71">
-        <v>-2.592456257016208</v>
+        <v>-3.693570187742119</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.644082192818068</v>
       </c>
       <c r="E72">
-        <v>-10.83625545677211</v>
+        <v>-12.20889027018509</v>
       </c>
       <c r="F72">
-        <v>-4.458062275426733</v>
+        <v>-4.389549664275991</v>
       </c>
       <c r="G72">
-        <v>-2.847431163905335</v>
+        <v>-3.732359849825759</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.479308837989484</v>
       </c>
       <c r="E73">
-        <v>-10.24848670142055</v>
+        <v>-12.36176702421004</v>
       </c>
       <c r="F73">
-        <v>-4.319357124032373</v>
+        <v>-4.144022394453621</v>
       </c>
       <c r="G73">
-        <v>-2.758476805265119</v>
+        <v>-3.933717161160851</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.310130359787481</v>
       </c>
       <c r="E74">
-        <v>-11.13560570257516</v>
+        <v>-12.25963182144104</v>
       </c>
       <c r="F74">
-        <v>-4.318447576624099</v>
+        <v>-4.409069313755559</v>
       </c>
       <c r="G74">
-        <v>-3.101945904964504</v>
+        <v>-3.262560332347785</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.143503932137794</v>
       </c>
       <c r="E75">
-        <v>-10.54093102436189</v>
+        <v>-13.01168455684287</v>
       </c>
       <c r="F75">
-        <v>-4.481462826188416</v>
+        <v>-4.365741556752131</v>
       </c>
       <c r="G75">
-        <v>-2.53548507883089</v>
+        <v>-3.340464089977915</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.98746486486114</v>
       </c>
       <c r="E76">
-        <v>-11.26747033720451</v>
+        <v>-13.26414245429649</v>
       </c>
       <c r="F76">
-        <v>-4.780174596740126</v>
+        <v>-4.578180519037078</v>
       </c>
       <c r="G76">
-        <v>-2.917502170789549</v>
+        <v>-3.113618888535974</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.845360788209574</v>
       </c>
       <c r="E77">
-        <v>-12.85771644058208</v>
+        <v>-13.83409619290188</v>
       </c>
       <c r="F77">
-        <v>-4.610208516298918</v>
+        <v>-4.678536401518835</v>
       </c>
       <c r="G77">
-        <v>-2.914429984529106</v>
+        <v>-3.577399834223554</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.720424031321635</v>
       </c>
       <c r="E78">
-        <v>-11.35052255050518</v>
+        <v>-14.09747224118798</v>
       </c>
       <c r="F78">
-        <v>-4.640591375898799</v>
+        <v>-4.790567294175649</v>
       </c>
       <c r="G78">
-        <v>-3.144552626054924</v>
+        <v>-3.374638851579811</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.613309143743471</v>
       </c>
       <c r="E79">
-        <v>-12.88998634636074</v>
+        <v>-14.85451535494627</v>
       </c>
       <c r="F79">
-        <v>-5.00877417868629</v>
+        <v>-4.868089229199238</v>
       </c>
       <c r="G79">
-        <v>-2.827918808496871</v>
+        <v>-3.084982669621279</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.52203366915112</v>
       </c>
       <c r="E80">
-        <v>-13.62756155036005</v>
+        <v>-15.70123131100444</v>
       </c>
       <c r="F80">
-        <v>-5.0251700546899</v>
+        <v>-4.973835298371012</v>
       </c>
       <c r="G80">
-        <v>-2.500244321565348</v>
+        <v>-2.978694294537438</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.445180113584177</v>
       </c>
       <c r="E81">
-        <v>-13.3561338752883</v>
+        <v>-16.60499245413724</v>
       </c>
       <c r="F81">
-        <v>-5.067895588591493</v>
+        <v>-4.999998454421031</v>
       </c>
       <c r="G81">
-        <v>-2.306057651868318</v>
+        <v>-2.713870514668979</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.380170089749417</v>
       </c>
       <c r="E82">
-        <v>-15.40622840024876</v>
+        <v>-17.4317468967696</v>
       </c>
       <c r="F82">
-        <v>-5.027254227075344</v>
+        <v>-4.757496382353684</v>
       </c>
       <c r="G82">
-        <v>-2.350538141733966</v>
+        <v>-2.908970894934848</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.322728938164765</v>
       </c>
       <c r="E83">
-        <v>-17.2956662528391</v>
+        <v>-16.80282336963633</v>
       </c>
       <c r="F83">
-        <v>-5.011412528864206</v>
+        <v>-5.142624268732842</v>
       </c>
       <c r="G83">
-        <v>-2.536640459224095</v>
+        <v>-3.066301261143171</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.269561341397728</v>
       </c>
       <c r="E84">
-        <v>-16.35828571867336</v>
+        <v>-18.00215348277576</v>
       </c>
       <c r="F84">
-        <v>-5.402134380314468</v>
+        <v>-5.246328412256714</v>
       </c>
       <c r="G84">
-        <v>-2.116330287012687</v>
+        <v>-3.033477202121297</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.215139383905607</v>
       </c>
       <c r="E85">
-        <v>-17.36985624250677</v>
+        <v>-18.93505988462192</v>
       </c>
       <c r="F85">
-        <v>-5.633311841618143</v>
+        <v>-5.615086102021748</v>
       </c>
       <c r="G85">
-        <v>-2.06189498671045</v>
+        <v>-2.977886521425856</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.151370412749045</v>
       </c>
       <c r="E86">
-        <v>-18.04277389462456</v>
+        <v>-19.50812468487058</v>
       </c>
       <c r="F86">
-        <v>-5.982599583947777</v>
+        <v>-5.44278816734166</v>
       </c>
       <c r="G86">
-        <v>-2.468410115659716</v>
+        <v>-2.195094786483026</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.073643457487438</v>
       </c>
       <c r="E87">
-        <v>-19.95034828561562</v>
+        <v>-21.69877398608112</v>
       </c>
       <c r="F87">
-        <v>-5.71287487392223</v>
+        <v>-5.847656877296932</v>
       </c>
       <c r="G87">
-        <v>-2.725752062609423</v>
+        <v>-3.510473845601647</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.977696310127499</v>
       </c>
       <c r="E88">
-        <v>-21.20503899349882</v>
+        <v>-21.25100300467668</v>
       </c>
       <c r="F88">
-        <v>-5.711603329958932</v>
+        <v>-5.406556205510612</v>
       </c>
       <c r="G88">
-        <v>-2.206373815135323</v>
+        <v>-2.789208599506173</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.865291447360183</v>
       </c>
       <c r="E89">
-        <v>-22.68685531523673</v>
+        <v>-24.04202833287614</v>
       </c>
       <c r="F89">
-        <v>-6.153246582394086</v>
+        <v>-5.62239230251444</v>
       </c>
       <c r="G89">
-        <v>-2.55061096139982</v>
+        <v>-2.953785749899962</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.743836637431518</v>
       </c>
       <c r="E90">
-        <v>-24.40406171589335</v>
+        <v>-25.04233201337846</v>
       </c>
       <c r="F90">
-        <v>-5.639310878349217</v>
+        <v>-5.937757571332031</v>
       </c>
       <c r="G90">
-        <v>-2.366117569041776</v>
+        <v>-2.657859394690049</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.623534315459416</v>
       </c>
       <c r="E91">
-        <v>-25.53659683741964</v>
+        <v>-26.9178357514472</v>
       </c>
       <c r="F91">
-        <v>-6.098947927507981</v>
+        <v>-5.483191787413205</v>
       </c>
       <c r="G91">
-        <v>-2.080960418471113</v>
+        <v>-3.521756184799484</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.517477710943484</v>
       </c>
       <c r="E92">
-        <v>-27.23008309122408</v>
+        <v>-28.47186764818543</v>
       </c>
       <c r="F92">
-        <v>-5.761437084543948</v>
+        <v>-5.566806364684385</v>
       </c>
       <c r="G92">
-        <v>-2.828491532875165</v>
+        <v>-3.561158297807889</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.441668406310463</v>
       </c>
       <c r="E93">
-        <v>-30.51159196766832</v>
+        <v>-31.01158531132921</v>
       </c>
       <c r="F93">
-        <v>-5.692777023995508</v>
+        <v>-5.830543635122496</v>
       </c>
       <c r="G93">
-        <v>-2.993257384364692</v>
+        <v>-3.839412960929172</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.412123784125571</v>
       </c>
       <c r="E94">
-        <v>-32.04989873841492</v>
+        <v>-32.73877473293574</v>
       </c>
       <c r="F94">
-        <v>-6.088687768856906</v>
+        <v>-5.592677107041216</v>
       </c>
       <c r="G94">
-        <v>-3.022827177121462</v>
+        <v>-4.282913504643176</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.447212293979237</v>
       </c>
       <c r="E95">
-        <v>-33.14796990850584</v>
+        <v>-35.04701718294045</v>
       </c>
       <c r="F95">
-        <v>-5.515222269777253</v>
+        <v>-5.491478774910812</v>
       </c>
       <c r="G95">
-        <v>-3.997978160623644</v>
+        <v>-4.169580288651765</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.569523038047656</v>
       </c>
       <c r="E96">
-        <v>-36.76492776130526</v>
+        <v>-36.18682956219708</v>
       </c>
       <c r="F96">
-        <v>-5.89744424330739</v>
+        <v>-5.413557566799073</v>
       </c>
       <c r="G96">
-        <v>-3.700045614816933</v>
+        <v>-4.936365535912219</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.781994387198747</v>
       </c>
       <c r="E97">
-        <v>-38.04615532687341</v>
+        <v>-40.0511598361395</v>
       </c>
       <c r="F97">
-        <v>-5.825259479460039</v>
+        <v>-5.481474581787202</v>
       </c>
       <c r="G97">
-        <v>-4.797478218903175</v>
+        <v>-4.987652507406608</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.105572814957313</v>
       </c>
       <c r="E98">
-        <v>-41.16559691129414</v>
+        <v>-41.58021719872543</v>
       </c>
       <c r="F98">
-        <v>-5.606037844880969</v>
+        <v>-5.271692193763033</v>
       </c>
       <c r="G98">
-        <v>-4.874345775779513</v>
+        <v>-6.082009614686866</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.51281093437052</v>
       </c>
       <c r="E99">
-        <v>-43.45702287307137</v>
+        <v>-43.93786756439084</v>
       </c>
       <c r="F99">
-        <v>-6.449013506828844</v>
+        <v>-5.33206940865088</v>
       </c>
       <c r="G99">
-        <v>-5.82244298113477</v>
+        <v>-6.318852663657406</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.028443038384333</v>
       </c>
       <c r="E100">
-        <v>-46.11816703825684</v>
+        <v>-46.26729874427744</v>
       </c>
       <c r="F100">
-        <v>-5.58516547143263</v>
+        <v>-5.364894295354214</v>
       </c>
       <c r="G100">
-        <v>-6.51074512529572</v>
+        <v>-6.505636953528625</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.575456954649585</v>
       </c>
       <c r="E101">
-        <v>-48.18725624744247</v>
+        <v>-47.67742026552591</v>
       </c>
       <c r="F101">
-        <v>-5.896583569575882</v>
+        <v>-5.05593147819286</v>
       </c>
       <c r="G101">
-        <v>-5.735782830553268</v>
+        <v>-6.00350002722305</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.231979853682891</v>
       </c>
       <c r="E102">
-        <v>-50.40270460443751</v>
+        <v>-50.27461332077505</v>
       </c>
       <c r="F102">
-        <v>-5.737772284580772</v>
+        <v>-4.971022991038508</v>
       </c>
       <c r="G102">
-        <v>-6.597693293339139</v>
+        <v>-7.38311360144015</v>
       </c>
     </row>
   </sheetData>
